--- a/data/topics_codebook.xlsx
+++ b/data/topics_codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523D45BA-CC82-4B98-A7BD-873873DFDC51}"/>
+  <xr:revisionPtr revIDLastSave="685" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE20814D-D13A-4A77-93A0-66F7A2B55A04}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29535" yWindow="0" windowWidth="9600" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="114">
   <si>
     <t>academicachievement</t>
   </si>
@@ -369,6 +369,18 @@
   </si>
   <si>
     <t>Meta analysis</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Artificial intelligence</t>
+  </si>
+  <si>
+    <t>artificialintelligenceforskills</t>
+  </si>
+  <si>
+    <t>AI for skills</t>
   </si>
 </sst>
 </file>
@@ -1408,6 +1420,18 @@
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>113</v>
+      </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
